--- a/output/pdf_financials_xlsx/PRG.xlsx
+++ b/output/pdf_financials_xlsx/PRG.xlsx
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.633358</v>
+        <v>-0.633358</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-1.822084</v>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.633358</v>
+        <v>-0.633358</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-1.822084</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.633358</v>
+        <v>-0.633358</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-1.822084</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5.277983</v>
+        <v>-5.277983</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>20.245378</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.633358</v>
+        <v>-0.633358</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.822084</v>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.633358</v>
+        <v>-0.633358</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.822084</v>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -5143,46 +5143,46 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.00225</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.57867</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.967702</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.430433</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.726132</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.694263</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.674263</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.864738</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.151718</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.070611</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.439108</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.439108</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.58306</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.965548</v>
       </c>
     </row>
     <row r="93">
@@ -8054,7 +8054,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -8588,7 +8592,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -9412,7 +9420,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.00225</v>
       </c>
@@ -23958,10 +23970,10 @@
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>0.633358</v>
+        <v>-0.633358</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>1.822084</v>
+        <v>-1.822084</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PRG.xlsx
+++ b/output/pdf_financials_xlsx/PRG.xlsx
@@ -841,40 +841,40 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.027451</v>
+        <v>0.654878</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.233972</v>
+        <v>1.858283</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.342432</v>
+        <v>1.418718</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.106898</v>
+        <v>1.336818</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.119614</v>
+        <v>0.79753</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.111976</v>
+        <v>1.761686</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.139941</v>
+        <v>2.299494</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.119375</v>
+        <v>1.116539</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.134035</v>
+        <v>0.97031</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.167902</v>
+        <v>1.700057</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.292132</v>
+        <v>2.492345</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.229267</v>
+        <v>1.21679</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.970366</v>
@@ -890,40 +890,40 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.027451</v>
+        <v>-0.654878</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.233972</v>
+        <v>-1.858283</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.342432</v>
+        <v>-1.418718</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.106898</v>
+        <v>-1.336818</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.119614</v>
+        <v>-0.79753</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.111976</v>
+        <v>-1.761686</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.139941</v>
+        <v>-2.299494</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.119375</v>
+        <v>-1.116539</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.134035</v>
+        <v>-0.97031</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.167902</v>
+        <v>-1.700057</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.292132</v>
+        <v>-2.492345</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.229267</v>
+        <v>-1.21679</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-0.970366</v>
@@ -939,46 +939,46 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00052</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.012199</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012136</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.008644000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001895</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.010051</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.019018</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.016339</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005188</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.007425</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.07298399999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.201844</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.158874</v>
       </c>
     </row>
     <row r="13">
@@ -1736,46 +1736,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.633358</v>
+        <v>-0.632838</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.822084</v>
+        <v>-1.834283</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.50658</v>
+        <v>-1.518716</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.402155</v>
+        <v>-1.410799</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.239351</v>
+        <v>-3.241246</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.751635</v>
+        <v>-1.761686</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.745133</v>
+        <v>-1.764151</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.9408840000000001</v>
+        <v>-0.957223</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.545688</v>
+        <v>-0.550876</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.717632</v>
+        <v>-1.725057</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.092295</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.358607</v>
+        <v>0.285623</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.768522</v>
+        <v>-0.970366</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.875842</v>
+        <v>-2.034716</v>
       </c>
     </row>
     <row r="28">
@@ -1834,46 +1834,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.633358</v>
+        <v>-0.632838</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.822084</v>
+        <v>-1.834283</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.50658</v>
+        <v>-1.518716</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.402155</v>
+        <v>-1.410799</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.239351</v>
+        <v>-3.241246</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.751635</v>
+        <v>-1.761686</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.745133</v>
+        <v>-1.764151</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.9408840000000001</v>
+        <v>-0.957223</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.545688</v>
+        <v>-0.550876</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.70018</v>
+        <v>-1.707605</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.073847</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.390284</v>
+        <v>0.3173</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.76503</v>
+        <v>-0.966874</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.873041</v>
+        <v>-2.031915</v>
       </c>
     </row>
     <row r="30">
@@ -2102,25 +2102,25 @@
         <v>0.789524</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.836607</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.957855</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.402117</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.551992</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.8389</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.399801</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.446345</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>6.640147</v>
@@ -2200,25 +2200,25 @@
         <v>0.789524</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.836607</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.957855</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.402117</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.551992</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.8389</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.399801</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.446345</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>6.640147</v>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -18607,16 +18607,16 @@
         </is>
       </c>
       <c r="N138" s="5" t="n">
-        <v>-1.700057</v>
+        <v>1.700057</v>
       </c>
       <c r="O138" s="5" t="n">
-        <v>-2.492345</v>
+        <v>2.492345</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>-1.21679</v>
+        <v>1.21679</v>
       </c>
       <c r="Q138" s="5" t="n">
-        <v>-0.970366</v>
+        <v>0.970366</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -20864,35 +20864,35 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
         <v>0.654878</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-1.858283</v>
+        <v>1.858283</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>-1.418718</v>
+        <v>1.418718</v>
       </c>
       <c r="H166" s="5" t="n">
-        <v>-1.336818</v>
+        <v>1.336818</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>-0.79753</v>
+        <v>0.79753</v>
       </c>
       <c r="J166" s="5" t="n">
-        <v>-1.761686</v>
+        <v>1.761686</v>
       </c>
       <c r="K166" s="5" t="n">
-        <v>-2.299494</v>
+        <v>2.299494</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>-1.116539</v>
+        <v>1.116539</v>
       </c>
       <c r="M166" s="5" t="n">
-        <v>-0.97031</v>
+        <v>0.97031</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">

--- a/output/pdf_financials_xlsx/PRG.xlsx
+++ b/output/pdf_financials_xlsx/PRG.xlsx
@@ -697,16 +697,16 @@
         <v>0.019284</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.229314</v>
+        <v>0.253314</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.30614</v>
+        <v>0.35414</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.096946</v>
+        <v>0.144946</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.09161</v>
+        <v>0.11961</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.106763</v>
@@ -715,25 +715,25 @@
         <v>0.12846</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.10589</v>
+        <v>0.12589</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.107382</v>
+        <v>0.112597</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.15347</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.279575</v>
+        <v>0.409575</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.228639</v>
+        <v>0.268639</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.2072</v>
+        <v>0.2472</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.209845</v>
+        <v>0.241845</v>
       </c>
     </row>
     <row r="8">
@@ -1168,7 +1168,7 @@
         <v>-0.092295</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.358607</v>
+        <v>1.959495</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-0.768522</v>
@@ -1217,7 +1217,7 @@
         <v>1.64366</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.600888</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0</v>
@@ -1769,7 +1769,7 @@
         <v>-0.092295</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.285623</v>
+        <v>1.886511</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.970366</v>
@@ -1867,7 +1867,7 @@
         <v>-0.073847</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.3173</v>
+        <v>1.918188</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.966874</v>
@@ -1993,7 +1993,7 @@
         <v>-1780.87653719053</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>81.6990091834886</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -6274,13 +6274,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.113343</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.041316</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.318434</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -13572,7 +13572,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -16798,7 +16802,11 @@
           <t>Consulting and directors’ fees (Note 8)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -18228,7 +18236,11 @@
           <t>Consulting and directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -19040,7 +19052,11 @@
           <t>Income tax recovery (Note 4, 12)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -21336,7 +21352,11 @@
           <t>Directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -21584,7 +21604,11 @@
           <t>Directors’ fees (Note 8)</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -22338,7 +22362,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -22844,7 +22872,11 @@
           <t>Directors fees (Note 8)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
